--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/7.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/7.xlsx
@@ -426,13 +426,13 @@
         <v>-14.41225814945746</v>
       </c>
       <c r="E2">
-        <v>-6.326176110520915</v>
+        <v>-6.483332272483107</v>
       </c>
       <c r="F2">
-        <v>-5.175199816847933</v>
+        <v>-4.355889783230636</v>
       </c>
       <c r="G2">
-        <v>-8.049970031597702</v>
+        <v>-9.846970566315035</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-15.23310785266717</v>
       </c>
       <c r="E3">
-        <v>-6.264670376548736</v>
+        <v>-7.548252748600876</v>
       </c>
       <c r="F3">
-        <v>-4.941422938634273</v>
+        <v>-4.011035463240786</v>
       </c>
       <c r="G3">
-        <v>-8.224882705165095</v>
+        <v>-9.613219566878174</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-16.40541286315489</v>
       </c>
       <c r="E4">
-        <v>-9.26857021090076</v>
+        <v>-6.653113819978684</v>
       </c>
       <c r="F4">
-        <v>-5.44029395309183</v>
+        <v>-3.771830293436581</v>
       </c>
       <c r="G4">
-        <v>-8.190933060659869</v>
+        <v>-9.330515530552111</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-17.77267507316218</v>
       </c>
       <c r="E5">
-        <v>-8.134739945808272</v>
+        <v>-8.125637713052853</v>
       </c>
       <c r="F5">
-        <v>-4.944042236361924</v>
+        <v>-3.874040890533206</v>
       </c>
       <c r="G5">
-        <v>-7.393372982066351</v>
+        <v>-8.610683750675141</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-19.26651274115405</v>
       </c>
       <c r="E6">
-        <v>-8.91541263693858</v>
+        <v>-9.766385358563962</v>
       </c>
       <c r="F6">
-        <v>-5.353873695427369</v>
+        <v>-3.663732489208259</v>
       </c>
       <c r="G6">
-        <v>-8.38584473983</v>
+        <v>-9.065301106310018</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-20.7662188742044</v>
       </c>
       <c r="E7">
-        <v>-8.709317256375494</v>
+        <v>-10.58889209257713</v>
       </c>
       <c r="F7">
-        <v>-4.690884046024965</v>
+        <v>-3.613097703344736</v>
       </c>
       <c r="G7">
-        <v>-7.282873593056558</v>
+        <v>-8.984874712978964</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-22.18180450101668</v>
       </c>
       <c r="E8">
-        <v>-10.12287136092178</v>
+        <v>-10.188534234033</v>
       </c>
       <c r="F8">
-        <v>-4.624125917033353</v>
+        <v>-3.832010356882562</v>
       </c>
       <c r="G8">
-        <v>-7.89676791567685</v>
+        <v>-8.807161317885347</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-23.39770015032787</v>
       </c>
       <c r="E9">
-        <v>-10.26893729003919</v>
+        <v>-11.29475892157473</v>
       </c>
       <c r="F9">
-        <v>-4.642050959262531</v>
+        <v>-3.445587732252829</v>
       </c>
       <c r="G9">
-        <v>-7.546846562721425</v>
+        <v>-9.258676692349926</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-24.32007924112451</v>
       </c>
       <c r="E10">
-        <v>-11.06611626892746</v>
+        <v>-11.9844273990469</v>
       </c>
       <c r="F10">
-        <v>-4.606663932182339</v>
+        <v>-3.288699087999617</v>
       </c>
       <c r="G10">
-        <v>-7.189145427748712</v>
+        <v>-9.116104738155673</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-24.87884714552462</v>
       </c>
       <c r="E11">
-        <v>-12.92998182879648</v>
+        <v>-12.62199125458681</v>
       </c>
       <c r="F11">
-        <v>-4.399417176778139</v>
+        <v>-3.060306597904153</v>
       </c>
       <c r="G11">
-        <v>-7.79129393479567</v>
+        <v>-9.16113808912638</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-25.02783872619189</v>
       </c>
       <c r="E12">
-        <v>-12.81948253453532</v>
+        <v>-13.02102227024669</v>
       </c>
       <c r="F12">
-        <v>-4.029221441201845</v>
+        <v>-2.858783032885896</v>
       </c>
       <c r="G12">
-        <v>-6.683234479528368</v>
+        <v>-8.274434950796907</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-24.73587058284781</v>
       </c>
       <c r="E13">
-        <v>-12.67321735256157</v>
+        <v>-14.22731717640992</v>
       </c>
       <c r="F13">
-        <v>-4.100654047447455</v>
+        <v>-2.588961403874221</v>
       </c>
       <c r="G13">
-        <v>-6.768716075897888</v>
+        <v>-8.303776315911467</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-24.00998085900155</v>
       </c>
       <c r="E14">
-        <v>-14.40705230977435</v>
+        <v>-15.59128901904622</v>
       </c>
       <c r="F14">
-        <v>-4.085721896644592</v>
+        <v>-2.309484324415515</v>
       </c>
       <c r="G14">
-        <v>-5.547869644653157</v>
+        <v>-7.744890017971705</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-22.88423246421899</v>
       </c>
       <c r="E15">
-        <v>-14.32142339476331</v>
+        <v>-15.47509743295742</v>
       </c>
       <c r="F15">
-        <v>-3.391492855747813</v>
+        <v>-2.395459748784673</v>
       </c>
       <c r="G15">
-        <v>-6.193075106983875</v>
+        <v>-7.423568467930044</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-21.40814038945008</v>
       </c>
       <c r="E16">
-        <v>-15.87296463079733</v>
+        <v>-16.48006091321363</v>
       </c>
       <c r="F16">
-        <v>-3.251270135271524</v>
+        <v>-2.082284683380084</v>
       </c>
       <c r="G16">
-        <v>-4.605016343432105</v>
+        <v>-7.115121629490608</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-19.65130739847458</v>
       </c>
       <c r="E17">
-        <v>-15.54803756379896</v>
+        <v>-17.59495310000604</v>
       </c>
       <c r="F17">
-        <v>-3.148981671639035</v>
+        <v>-2.053954518204341</v>
       </c>
       <c r="G17">
-        <v>-4.921011225701079</v>
+        <v>-6.221403445163419</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-17.7100320175744</v>
       </c>
       <c r="E18">
-        <v>-16.60217121483046</v>
+        <v>-18.52329932852648</v>
       </c>
       <c r="F18">
-        <v>-2.797901342249743</v>
+        <v>-1.38993023791584</v>
       </c>
       <c r="G18">
-        <v>-4.019814519000676</v>
+        <v>-6.56703102055441</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-15.69007066730741</v>
       </c>
       <c r="E19">
-        <v>-17.94132701990473</v>
+        <v>-18.94707845463828</v>
       </c>
       <c r="F19">
-        <v>-2.499650972341392</v>
+        <v>-1.041059992757217</v>
       </c>
       <c r="G19">
-        <v>-3.568087269621584</v>
+        <v>-5.759085760604198</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-13.69108852629064</v>
       </c>
       <c r="E20">
-        <v>-19.42168064453816</v>
+        <v>-19.43791522385566</v>
       </c>
       <c r="F20">
-        <v>-2.311398681483385</v>
+        <v>-0.9565491219562089</v>
       </c>
       <c r="G20">
-        <v>-3.585219342787312</v>
+        <v>-5.385831682687989</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-11.82460870852598</v>
       </c>
       <c r="E21">
-        <v>-19.01175864888983</v>
+        <v>-20.81751030181843</v>
       </c>
       <c r="F21">
-        <v>-2.222646569580043</v>
+        <v>-0.6608327279330217</v>
       </c>
       <c r="G21">
-        <v>-3.836744661224519</v>
+        <v>-5.28103636364236</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-10.18972136651526</v>
       </c>
       <c r="E22">
-        <v>-20.77453961195964</v>
+        <v>-21.2380877968068</v>
       </c>
       <c r="F22">
-        <v>-2.04817831230462</v>
+        <v>0.08371631921421588</v>
       </c>
       <c r="G22">
-        <v>-3.846845135664835</v>
+        <v>-5.027488301880658</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-8.855818798547315</v>
       </c>
       <c r="E23">
-        <v>-21.04268414337583</v>
+        <v>-22.08178326070186</v>
       </c>
       <c r="F23">
-        <v>-2.186903344516647</v>
+        <v>-0.3069284940675862</v>
       </c>
       <c r="G23">
-        <v>-3.116158076964596</v>
+        <v>-4.682142122860506</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-7.868720956441361</v>
       </c>
       <c r="E24">
-        <v>-20.98692957139339</v>
+        <v>-22.9043307509811</v>
       </c>
       <c r="F24">
-        <v>-1.358249326595773</v>
+        <v>0.1558190746886904</v>
       </c>
       <c r="G24">
-        <v>-4.006022786284072</v>
+        <v>-4.629746118610461</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-7.259614368743208</v>
       </c>
       <c r="E25">
-        <v>-21.63874906310945</v>
+        <v>-22.74828859362479</v>
       </c>
       <c r="F25">
-        <v>-1.279956181520178</v>
+        <v>-0.06628030824770459</v>
       </c>
       <c r="G25">
-        <v>-4.420827521263674</v>
+        <v>-5.395756698214725</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-7.029009985093529</v>
       </c>
       <c r="E26">
-        <v>-21.69174579442121</v>
+        <v>-22.77961657680985</v>
       </c>
       <c r="F26">
-        <v>-0.9187407769576338</v>
+        <v>-0.09029799272447346</v>
       </c>
       <c r="G26">
-        <v>-3.960595480394193</v>
+        <v>-5.198461426256318</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-7.143061898521607</v>
       </c>
       <c r="E27">
-        <v>-22.47560200277891</v>
+        <v>-23.61715784452849</v>
       </c>
       <c r="F27">
-        <v>-0.8328713836160343</v>
+        <v>0.1511611647827488</v>
       </c>
       <c r="G27">
-        <v>-5.190039398404413</v>
+        <v>-4.879506916275236</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-7.563041007628835</v>
       </c>
       <c r="E28">
-        <v>-22.30980098393608</v>
+        <v>-23.51131382154721</v>
       </c>
       <c r="F28">
-        <v>-1.102248179332405</v>
+        <v>-0.0465013797710608</v>
       </c>
       <c r="G28">
-        <v>-5.423969167300394</v>
+        <v>-5.076818740961338</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-8.238211846159583</v>
       </c>
       <c r="E29">
-        <v>-22.22032739449253</v>
+        <v>-23.10569387620617</v>
       </c>
       <c r="F29">
-        <v>-1.118127154076669</v>
+        <v>-0.02820688568023372</v>
       </c>
       <c r="G29">
-        <v>-4.608177914422109</v>
+        <v>-5.927635565645112</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-9.099917282939346</v>
       </c>
       <c r="E30">
-        <v>-22.12865749515526</v>
+        <v>-22.85071361873028</v>
       </c>
       <c r="F30">
-        <v>-1.472430661030254</v>
+        <v>0.1224979959110803</v>
       </c>
       <c r="G30">
-        <v>-5.097622209130118</v>
+        <v>-5.672187250743868</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-10.07900804158351</v>
       </c>
       <c r="E31">
-        <v>-20.87668840015066</v>
+        <v>-22.89442697832632</v>
       </c>
       <c r="F31">
-        <v>-1.13807092766647</v>
+        <v>-0.01871959381597098</v>
       </c>
       <c r="G31">
-        <v>-4.833635997283094</v>
+        <v>-5.928248016569877</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-11.12210294151689</v>
       </c>
       <c r="E32">
-        <v>-22.01420484308539</v>
+        <v>-23.50511886910472</v>
       </c>
       <c r="F32">
-        <v>-1.253414461567079</v>
+        <v>-0.1820827576894643</v>
       </c>
       <c r="G32">
-        <v>-5.070104954607696</v>
+        <v>-5.947147921053576</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-12.17822566806623</v>
       </c>
       <c r="E33">
-        <v>-20.84094062633411</v>
+        <v>-22.1964578079981</v>
       </c>
       <c r="F33">
-        <v>-1.19878611645466</v>
+        <v>-0.06665141684415878</v>
       </c>
       <c r="G33">
-        <v>-5.559704844956051</v>
+        <v>-6.292103455700095</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-13.19889029188844</v>
       </c>
       <c r="E34">
-        <v>-19.41587966933434</v>
+        <v>-21.95432030280796</v>
       </c>
       <c r="F34">
-        <v>-1.722894172205907</v>
+        <v>-0.1929120047462622</v>
       </c>
       <c r="G34">
-        <v>-5.593707458189906</v>
+        <v>-5.559565802043402</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-14.15180488419022</v>
       </c>
       <c r="E35">
-        <v>-20.15237256804581</v>
+        <v>-21.50309409573567</v>
       </c>
       <c r="F35">
-        <v>-1.247406312794574</v>
+        <v>-0.006634541776528993</v>
       </c>
       <c r="G35">
-        <v>-5.117535140548834</v>
+        <v>-6.217013661778346</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-15.02012815555348</v>
       </c>
       <c r="E36">
-        <v>-19.51419284004086</v>
+        <v>-20.69312217777574</v>
       </c>
       <c r="F36">
-        <v>-0.966410835886537</v>
+        <v>-0.1330558329547755</v>
       </c>
       <c r="G36">
-        <v>-5.002871085250638</v>
+        <v>-6.292934402630451</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-15.78518741465896</v>
       </c>
       <c r="E37">
-        <v>-20.16149744317127</v>
+        <v>-20.50420329912374</v>
       </c>
       <c r="F37">
-        <v>-1.636784552317496</v>
+        <v>-0.09100790358867264</v>
       </c>
       <c r="G37">
-        <v>-5.11582689905057</v>
+        <v>-5.992230930207371</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-16.43091892871328</v>
       </c>
       <c r="E38">
-        <v>-18.71657912764786</v>
+        <v>-20.42390439801973</v>
       </c>
       <c r="F38">
-        <v>-1.03476108702633</v>
+        <v>-0.1809222149581422</v>
       </c>
       <c r="G38">
-        <v>-5.310096332386082</v>
+        <v>-5.356477075391272</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-16.95431100901274</v>
       </c>
       <c r="E39">
-        <v>-18.10210143259905</v>
+        <v>-19.75719075529245</v>
       </c>
       <c r="F39">
-        <v>-0.9965766632268838</v>
+        <v>-0.4278800752851476</v>
       </c>
       <c r="G39">
-        <v>-5.225064970209901</v>
+        <v>-4.603347828480312</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-17.34964808459953</v>
       </c>
       <c r="E40">
-        <v>-18.031226285905</v>
+        <v>-19.23892954748462</v>
       </c>
       <c r="F40">
-        <v>-1.310611573995579</v>
+        <v>-0.4761714097661504</v>
       </c>
       <c r="G40">
-        <v>-4.63297390051125</v>
+        <v>-4.777614945667548</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-17.60639596924611</v>
       </c>
       <c r="E41">
-        <v>-17.23298764409894</v>
+        <v>-19.44926810819289</v>
       </c>
       <c r="F41">
-        <v>-1.104858365018627</v>
+        <v>-0.3484653207461618</v>
       </c>
       <c r="G41">
-        <v>-4.04764296480379</v>
+        <v>-4.507669751849836</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-17.72176667560959</v>
       </c>
       <c r="E42">
-        <v>-15.73236909828118</v>
+        <v>-18.60958034379462</v>
       </c>
       <c r="F42">
-        <v>-1.708756425742328</v>
+        <v>-0.5817915670926985</v>
       </c>
       <c r="G42">
-        <v>-4.131369972037498</v>
+        <v>-4.619059677609693</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-17.69823944663587</v>
       </c>
       <c r="E43">
-        <v>-15.41147237314965</v>
+        <v>-17.76989710787036</v>
       </c>
       <c r="F43">
-        <v>-1.751157239622023</v>
+        <v>-0.3238420996979465</v>
       </c>
       <c r="G43">
-        <v>-4.025409340962045</v>
+        <v>-4.502866150272353</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-17.53126630075286</v>
       </c>
       <c r="E44">
-        <v>-16.35919594194891</v>
+        <v>-17.46588706231343</v>
       </c>
       <c r="F44">
-        <v>-1.350710354862895</v>
+        <v>-0.4846903401365405</v>
       </c>
       <c r="G44">
-        <v>-3.652718055787513</v>
+        <v>-4.473958466623437</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-17.21923524302871</v>
       </c>
       <c r="E45">
-        <v>-15.21080663292176</v>
+        <v>-16.01593308369349</v>
       </c>
       <c r="F45">
-        <v>-2.052283701152894</v>
+        <v>-0.6429217679496908</v>
       </c>
       <c r="G45">
-        <v>-4.153507590058604</v>
+        <v>-4.331502381523059</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-16.77252153129872</v>
       </c>
       <c r="E46">
-        <v>-15.51317737088791</v>
+        <v>-16.41255495118128</v>
       </c>
       <c r="F46">
-        <v>-2.002823540266541</v>
+        <v>-0.7609873171358987</v>
       </c>
       <c r="G46">
-        <v>-3.845103788711179</v>
+        <v>-4.274302775695531</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-16.20265035730419</v>
       </c>
       <c r="E47">
-        <v>-15.02640264285541</v>
+        <v>-16.10371755233217</v>
       </c>
       <c r="F47">
-        <v>-1.910777839569669</v>
+        <v>-1.094930381696075</v>
       </c>
       <c r="G47">
-        <v>-4.126827903557618</v>
+        <v>-4.347498937568817</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-15.52136519633198</v>
       </c>
       <c r="E48">
-        <v>-13.19108911160475</v>
+        <v>-14.72402284794124</v>
       </c>
       <c r="F48">
-        <v>-2.004205257094411</v>
+        <v>-1.216376498253107</v>
       </c>
       <c r="G48">
-        <v>-4.285098464699095</v>
+        <v>-3.34502933227657</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-14.75789150819395</v>
       </c>
       <c r="E49">
-        <v>-12.51681744575866</v>
+        <v>-15.02666529434786</v>
       </c>
       <c r="F49">
-        <v>-2.055372683197934</v>
+        <v>-1.250427368712584</v>
       </c>
       <c r="G49">
-        <v>-3.683449850028567</v>
+        <v>-3.94180482391329</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-13.94809393876914</v>
       </c>
       <c r="E50">
-        <v>-11.67674928954375</v>
+        <v>-13.7288454000156</v>
       </c>
       <c r="F50">
-        <v>-2.286806110029073</v>
+        <v>-1.293632527340398</v>
       </c>
       <c r="G50">
-        <v>-3.881877328561403</v>
+        <v>-3.494550121557753</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-13.1239582772046</v>
       </c>
       <c r="E51">
-        <v>-12.57854960343122</v>
+        <v>-14.04242863962475</v>
       </c>
       <c r="F51">
-        <v>-2.490886016852371</v>
+        <v>-1.428205782129594</v>
       </c>
       <c r="G51">
-        <v>-3.341063298720523</v>
+        <v>-3.755954107884145</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-12.32388599819938</v>
       </c>
       <c r="E52">
-        <v>-11.67942561768228</v>
+        <v>-13.36899926994409</v>
       </c>
       <c r="F52">
-        <v>-2.267494380767609</v>
+        <v>-1.234843292763717</v>
       </c>
       <c r="G52">
-        <v>-3.147333484307912</v>
+        <v>-3.512350924922414</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-11.59657932045837</v>
       </c>
       <c r="E53">
-        <v>-11.45701414526956</v>
+        <v>-12.62874773780625</v>
       </c>
       <c r="F53">
-        <v>-2.558993556343143</v>
+        <v>-1.339789987391789</v>
       </c>
       <c r="G53">
-        <v>-3.656065017327716</v>
+        <v>-3.849976911744986</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-10.98246446476125</v>
       </c>
       <c r="E54">
-        <v>-11.78339485242439</v>
+        <v>-12.89208302982629</v>
       </c>
       <c r="F54">
-        <v>-2.226002285928784</v>
+        <v>-1.570835738278419</v>
       </c>
       <c r="G54">
-        <v>-3.484118592563509</v>
+        <v>-4.164263552515696</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-10.509899408288</v>
       </c>
       <c r="E55">
-        <v>-9.738707325429081</v>
+        <v>-12.33657965177937</v>
       </c>
       <c r="F55">
-        <v>-2.770680361026348</v>
+        <v>-1.325008599456235</v>
       </c>
       <c r="G55">
-        <v>-4.378869667098951</v>
+        <v>-4.449020127076107</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-10.21054889523151</v>
       </c>
       <c r="E56">
-        <v>-10.84599167588861</v>
+        <v>-11.6276606313006</v>
       </c>
       <c r="F56">
-        <v>-2.716653410648362</v>
+        <v>-1.712968673985563</v>
       </c>
       <c r="G56">
-        <v>-4.420294523431851</v>
+        <v>-4.147561850270073</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-10.1061390414235</v>
       </c>
       <c r="E57">
-        <v>-9.435154655746922</v>
+        <v>-10.64055292405663</v>
       </c>
       <c r="F57">
-        <v>-2.769179359292476</v>
+        <v>-1.795151832384705</v>
       </c>
       <c r="G57">
-        <v>-4.163233972852983</v>
+        <v>-4.270724075967579</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-10.19697767728426</v>
       </c>
       <c r="E58">
-        <v>-9.431482063326701</v>
+        <v>-10.91781327365026</v>
       </c>
       <c r="F58">
-        <v>-2.375089365982431</v>
+        <v>-1.887231496145093</v>
       </c>
       <c r="G58">
-        <v>-4.938053914137247</v>
+        <v>-4.153348683872719</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-10.47271974525402</v>
       </c>
       <c r="E59">
-        <v>-7.992074900670625</v>
+        <v>-10.13343176230767</v>
       </c>
       <c r="F59">
-        <v>-2.574083096952539</v>
+        <v>-1.613575354425859</v>
       </c>
       <c r="G59">
-        <v>-4.362081890669307</v>
+        <v>-3.829242965032531</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-10.92185086260185</v>
       </c>
       <c r="E60">
-        <v>-7.675385127892214</v>
+        <v>-10.28179815622097</v>
       </c>
       <c r="F60">
-        <v>-2.905106166417847</v>
+        <v>-1.921773588474429</v>
       </c>
       <c r="G60">
-        <v>-3.662262358577231</v>
+        <v>-4.183289257729887</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-11.51506326198366</v>
       </c>
       <c r="E61">
-        <v>-8.26509659859307</v>
+        <v>-9.992867929109581</v>
       </c>
       <c r="F61">
-        <v>-2.905027471514581</v>
+        <v>-2.029585605948785</v>
       </c>
       <c r="G61">
-        <v>-3.93971586967801</v>
+        <v>-4.53118124626974</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-12.21090558376678</v>
       </c>
       <c r="E62">
-        <v>-7.228999859534124</v>
+        <v>-9.183362443972435</v>
       </c>
       <c r="F62">
-        <v>-2.686404746567735</v>
+        <v>-2.009122445997429</v>
       </c>
       <c r="G62">
-        <v>-3.702631150883104</v>
+        <v>-4.538663079188493</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-12.9740220628202</v>
       </c>
       <c r="E63">
-        <v>-8.896379460684342</v>
+        <v>-9.9031996152837</v>
       </c>
       <c r="F63">
-        <v>-2.917201987233525</v>
+        <v>-1.993839895783181</v>
       </c>
       <c r="G63">
-        <v>-5.426200474993862</v>
+        <v>-4.987390974309005</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-13.76831211627192</v>
       </c>
       <c r="E64">
-        <v>-8.296578549894395</v>
+        <v>-9.089410193735297</v>
       </c>
       <c r="F64">
-        <v>-3.101385337408981</v>
+        <v>-2.079429300942634</v>
       </c>
       <c r="G64">
-        <v>-5.312201839349059</v>
+        <v>-4.937295799208754</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-14.54857969722418</v>
       </c>
       <c r="E65">
-        <v>-7.207824715074257</v>
+        <v>-8.818942555153178</v>
       </c>
       <c r="F65">
-        <v>-3.18909204964999</v>
+        <v>-2.330447818278162</v>
       </c>
       <c r="G65">
-        <v>-4.71977971509648</v>
+        <v>-5.010597898539297</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-15.27236578170349</v>
       </c>
       <c r="E66">
-        <v>-6.674424818658781</v>
+        <v>-9.362074142211139</v>
       </c>
       <c r="F66">
-        <v>-3.006933229406976</v>
+        <v>-2.404208136925639</v>
       </c>
       <c r="G66">
-        <v>-5.190161888589365</v>
+        <v>-4.928738038989738</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-15.91327153040068</v>
       </c>
       <c r="E67">
-        <v>-5.664724554590544</v>
+        <v>-8.575872184317465</v>
       </c>
       <c r="F67">
-        <v>-3.389026805989679</v>
+        <v>-2.108341808402545</v>
       </c>
       <c r="G67">
-        <v>-5.113678354995583</v>
+        <v>-5.436257912342168</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-16.44542626964499</v>
       </c>
       <c r="E68">
-        <v>-7.281321848218747</v>
+        <v>-9.240362346306982</v>
       </c>
       <c r="F68">
-        <v>-3.081563333827392</v>
+        <v>-1.887060024092713</v>
       </c>
       <c r="G68">
-        <v>-4.954186202550115</v>
+        <v>-5.551345717469392</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-16.84766484056821</v>
       </c>
       <c r="E69">
-        <v>-6.451882020499836</v>
+        <v>-7.618448624193774</v>
       </c>
       <c r="F69">
-        <v>-3.659053041749845</v>
+        <v>-2.662130268196099</v>
       </c>
       <c r="G69">
-        <v>-4.831600011776443</v>
+        <v>-5.193452570855401</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-17.117014153731</v>
       </c>
       <c r="E70">
-        <v>-6.461998631432972</v>
+        <v>-7.5986863636243</v>
       </c>
       <c r="F70">
-        <v>-3.155519975549332</v>
+        <v>-2.171664697774748</v>
       </c>
       <c r="G70">
-        <v>-4.463695775451696</v>
+        <v>-5.322438046156485</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-17.26103679861653</v>
       </c>
       <c r="E71">
-        <v>-7.660798913113507</v>
+        <v>-8.143507071487122</v>
       </c>
       <c r="F71">
-        <v>-3.800123182079198</v>
+        <v>-2.869413471766022</v>
       </c>
       <c r="G71">
-        <v>-4.630788940455331</v>
+        <v>-4.964806432640097</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-17.28772749985174</v>
       </c>
       <c r="E72">
-        <v>-6.970107000515609</v>
+        <v>-7.875321783804868</v>
       </c>
       <c r="F72">
-        <v>-3.646327661708039</v>
+        <v>-2.38260182995842</v>
       </c>
       <c r="G72">
-        <v>-4.328473232354626</v>
+        <v>-4.563922541653132</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-17.21378420602361</v>
       </c>
       <c r="E73">
-        <v>-6.66651357456738</v>
+        <v>-8.227374410109176</v>
       </c>
       <c r="F73">
-        <v>-3.576357952295773</v>
+        <v>-2.548566895844106</v>
       </c>
       <c r="G73">
-        <v>-4.722312282434022</v>
+        <v>-4.646292225215738</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-17.07108813895374</v>
       </c>
       <c r="E74">
-        <v>-6.816881553992075</v>
+        <v>-7.9178486832109</v>
       </c>
       <c r="F74">
-        <v>-3.837258064379297</v>
+        <v>-2.489492702880862</v>
       </c>
       <c r="G74">
-        <v>-4.465523196589374</v>
+        <v>-4.289087672073916</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-16.88542855080063</v>
       </c>
       <c r="E75">
-        <v>-5.819969700521499</v>
+        <v>-9.148239599568944</v>
       </c>
       <c r="F75">
-        <v>-3.615374885335032</v>
+        <v>-2.697635751814891</v>
       </c>
       <c r="G75">
-        <v>-3.275554223589424</v>
+        <v>-4.274786115344265</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-16.6764991079921</v>
       </c>
       <c r="E76">
-        <v>-7.182306764041035</v>
+        <v>-8.385966098331799</v>
       </c>
       <c r="F76">
-        <v>-4.146442884004601</v>
+        <v>-2.958396698174745</v>
       </c>
       <c r="G76">
-        <v>-3.79704128857204</v>
+        <v>-3.777482585526025</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-16.47190841225542</v>
       </c>
       <c r="E77">
-        <v>-8.137565713589058</v>
+        <v>-8.777004357368144</v>
       </c>
       <c r="F77">
-        <v>-3.547371720137013</v>
+        <v>-2.873663824909786</v>
       </c>
       <c r="G77">
-        <v>-4.265503345652149</v>
+        <v>-3.647434425106836</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-16.29436634626937</v>
       </c>
       <c r="E78">
-        <v>-7.666228553448704</v>
+        <v>-9.520919424978191</v>
       </c>
       <c r="F78">
-        <v>-4.1834593097661</v>
+        <v>-3.096396908909322</v>
       </c>
       <c r="G78">
-        <v>-4.69779438217018</v>
+        <v>-3.054820289212979</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-16.15073484721046</v>
       </c>
       <c r="E79">
-        <v>-8.414169434451571</v>
+        <v>-10.20079281317176</v>
       </c>
       <c r="F79">
-        <v>-4.249979697313108</v>
+        <v>-3.339794446139096</v>
       </c>
       <c r="G79">
-        <v>-2.971540205627073</v>
+        <v>-3.206509485822385</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-16.04590803452315</v>
       </c>
       <c r="E80">
-        <v>-9.788131090748795</v>
+        <v>-10.64093331587328</v>
       </c>
       <c r="F80">
-        <v>-4.441363216953698</v>
+        <v>-3.098959049286182</v>
       </c>
       <c r="G80">
-        <v>-2.295086503951173</v>
+        <v>-2.901128212552314</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-15.99052160500418</v>
       </c>
       <c r="E81">
-        <v>-10.76773964503606</v>
+        <v>-11.54637905133693</v>
       </c>
       <c r="F81">
-        <v>-4.175878091295679</v>
+        <v>-3.266576708140453</v>
       </c>
       <c r="G81">
-        <v>-3.427286457290841</v>
+        <v>-2.629130480500254</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-15.98042397193224</v>
       </c>
       <c r="E82">
-        <v>-11.18782806483161</v>
+        <v>-11.74324993034639</v>
       </c>
       <c r="F82">
-        <v>-4.341757006971474</v>
+        <v>-3.081278375440829</v>
       </c>
       <c r="G82">
-        <v>-1.600593639631785</v>
+        <v>-2.33334978929407</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-16.00335998536725</v>
       </c>
       <c r="E83">
-        <v>-12.83560390200262</v>
+        <v>-12.30731665274181</v>
       </c>
       <c r="F83">
-        <v>-4.299002480210783</v>
+        <v>-3.703673880269043</v>
       </c>
       <c r="G83">
-        <v>-1.522077431076891</v>
+        <v>-2.077745878752481</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-16.05790059359153</v>
       </c>
       <c r="E84">
-        <v>-12.62371207470972</v>
+        <v>-13.21942377347074</v>
       </c>
       <c r="F84">
-        <v>-4.537665069366154</v>
+        <v>-3.461585163535693</v>
       </c>
       <c r="G84">
-        <v>-2.112797934922284</v>
+        <v>-1.865278376587595</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-16.14106966116755</v>
       </c>
       <c r="E85">
-        <v>-13.81171194588196</v>
+        <v>-14.15824889084493</v>
       </c>
       <c r="F85">
-        <v>-4.716941999414829</v>
+        <v>-3.958886421764945</v>
       </c>
       <c r="G85">
-        <v>-2.45689934881967</v>
+        <v>-1.625939176280445</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-16.23967738492572</v>
       </c>
       <c r="E86">
-        <v>-15.33532608271067</v>
+        <v>-15.43001194573705</v>
       </c>
       <c r="F86">
-        <v>-5.063186319906578</v>
+        <v>-3.693573596526709</v>
       </c>
       <c r="G86">
-        <v>-2.435615851547696</v>
+        <v>-1.511026830066803</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-16.34575833221697</v>
       </c>
       <c r="E87">
-        <v>-17.67821362311107</v>
+        <v>-16.68609742361462</v>
       </c>
       <c r="F87">
-        <v>-4.728667540001456</v>
+        <v>-3.87536462164288</v>
       </c>
       <c r="G87">
-        <v>-2.433023694390447</v>
+        <v>-2.009124890814467</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-16.4633714320758</v>
       </c>
       <c r="E88">
-        <v>-17.45130990448273</v>
+        <v>-17.97922581887492</v>
       </c>
       <c r="F88">
-        <v>-4.770860433663048</v>
+        <v>-3.937981741987897</v>
       </c>
       <c r="G88">
-        <v>-2.291540909678614</v>
+        <v>-1.461418305160824</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-16.58674509822179</v>
       </c>
       <c r="E89">
-        <v>-18.95180165302828</v>
+        <v>-19.13285457232895</v>
       </c>
       <c r="F89">
-        <v>-5.262537905594695</v>
+        <v>-4.227342072929404</v>
       </c>
       <c r="G89">
-        <v>-2.351504821031433</v>
+        <v>-1.138693083810512</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-16.70775001628397</v>
       </c>
       <c r="E90">
-        <v>-20.32110350957161</v>
+        <v>-21.36013922826153</v>
       </c>
       <c r="F90">
-        <v>-5.092875007622911</v>
+        <v>-4.377443903051479</v>
       </c>
       <c r="G90">
-        <v>-2.234702153314867</v>
+        <v>-1.296357815118302</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-16.83331100468293</v>
       </c>
       <c r="E91">
-        <v>-22.53369779582331</v>
+        <v>-21.79134052327191</v>
       </c>
       <c r="F91">
-        <v>-5.130380170152062</v>
+        <v>-4.36519069242927</v>
       </c>
       <c r="G91">
-        <v>-2.015550659706193</v>
+        <v>-1.475653650979691</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-16.97219717415626</v>
       </c>
       <c r="E92">
-        <v>-25.01967152944408</v>
+        <v>-24.74980164943097</v>
       </c>
       <c r="F92">
-        <v>-5.748688510214864</v>
+        <v>-4.385808757084949</v>
       </c>
       <c r="G92">
-        <v>-2.489144062372172</v>
+        <v>-1.87406787499436</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-17.12465210616288</v>
       </c>
       <c r="E93">
-        <v>-26.92334690431453</v>
+        <v>-26.21845369722858</v>
       </c>
       <c r="F93">
-        <v>-5.523160514598281</v>
+        <v>-4.962658965372441</v>
       </c>
       <c r="G93">
-        <v>-2.308222748651001</v>
+        <v>-2.14615830232152</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-17.29629984926921</v>
       </c>
       <c r="E94">
-        <v>-28.07145997642721</v>
+        <v>-28.46157442676599</v>
       </c>
       <c r="F94">
-        <v>-6.16309504244597</v>
+        <v>-4.683844579835974</v>
       </c>
       <c r="G94">
-        <v>-2.915870071838689</v>
+        <v>-2.513334218627627</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-17.50297936543949</v>
       </c>
       <c r="E95">
-        <v>-30.49620874146427</v>
+        <v>-30.46229952809483</v>
       </c>
       <c r="F95">
-        <v>-5.225191789606883</v>
+        <v>-4.63106100892959</v>
       </c>
       <c r="G95">
-        <v>-2.560618740565037</v>
+        <v>-2.070244182560492</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-17.74719421659322</v>
       </c>
       <c r="E96">
-        <v>-33.73825875964267</v>
+        <v>-32.35737985929873</v>
       </c>
       <c r="F96">
-        <v>-5.604182301898699</v>
+        <v>-5.003147907286475</v>
       </c>
       <c r="G96">
-        <v>-3.657200534447686</v>
+        <v>-2.97100720779525</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-18.01668415453874</v>
       </c>
       <c r="E97">
-        <v>-34.98359137598902</v>
+        <v>-35.23611720055275</v>
       </c>
       <c r="F97">
-        <v>-5.693645981401045</v>
+        <v>-5.227160818923337</v>
       </c>
       <c r="G97">
-        <v>-3.960863634582874</v>
+        <v>-3.011975208843731</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-18.31675833834561</v>
       </c>
       <c r="E98">
-        <v>-38.38372136482718</v>
+        <v>-38.46349496294631</v>
       </c>
       <c r="F98">
-        <v>-5.923662071605995</v>
+        <v>-5.087321632554544</v>
       </c>
       <c r="G98">
-        <v>-5.135408775915359</v>
+        <v>-3.908520599061458</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-18.63251460205691</v>
       </c>
       <c r="E99">
-        <v>-40.58506918588084</v>
+        <v>-39.61655539291237</v>
       </c>
       <c r="F99">
-        <v>-6.538520261436136</v>
+        <v>-5.357268345044041</v>
       </c>
       <c r="G99">
-        <v>-4.98373613203365</v>
+        <v>-4.295582962421967</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-18.96097569427081</v>
       </c>
       <c r="E100">
-        <v>-42.80387427423407</v>
+        <v>-41.97222907967342</v>
       </c>
       <c r="F100">
-        <v>-6.182010812088897</v>
+        <v>-5.432261274386883</v>
       </c>
       <c r="G100">
-        <v>-4.761082081244427</v>
+        <v>-4.561876624509862</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-19.2694715538286</v>
       </c>
       <c r="E101">
-        <v>-45.2121982640453</v>
+        <v>-44.2000367743539</v>
       </c>
       <c r="F101">
-        <v>-6.174056828287215</v>
+        <v>-5.551751615505906</v>
       </c>
       <c r="G101">
-        <v>-5.20540364025217</v>
+        <v>-4.611548049781087</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-19.60379023234931</v>
       </c>
       <c r="E102">
-        <v>-47.36316907600063</v>
+        <v>-46.93928805922366</v>
       </c>
       <c r="F102">
-        <v>-6.515673474283225</v>
+        <v>-5.500432598167672</v>
       </c>
       <c r="G102">
-        <v>-6.507848397948859</v>
+        <v>-5.483376907002615</v>
       </c>
     </row>
   </sheetData>
